--- a/products/pack2-proposal-toolkit/pricing-volume-checklist.xlsx
+++ b/products/pack2-proposal-toolkit/pricing-volume-checklist.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -128,6 +128,21 @@
       <color rgb="FF999999"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -233,7 +248,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -396,6 +411,12 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="B2:I51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="27" min="1" max="1"/>
@@ -706,7 +727,6 @@
     <col width="30" customWidth="1" style="27" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1" s="28">
       <c r="B2" s="29" t="inlineStr">
         <is>
@@ -721,7 +741,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="28">
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -756,8 +775,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8" ht="36" customHeight="1" s="28">
       <c r="B8" s="36" t="inlineStr">
         <is>
@@ -1875,6 +1892,20 @@
       <c r="H48" s="38" t="inlineStr">
         <is>
           <t>Total hours by LCAT must reconcile exactly between Price and Management volumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="56" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="57" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="B2:M49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="27" min="1" max="1"/>
@@ -1927,7 +1958,6 @@
     <col width="16" customWidth="1" style="27" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1" s="28">
       <c r="B2" s="29" t="inlineStr">
         <is>
@@ -1949,7 +1979,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="36" customHeight="1" s="28">
       <c r="B6" s="36" t="inlineStr">
         <is>
@@ -2474,7 +2503,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="30" customHeight="1" s="28">
       <c r="B21" s="44" t="inlineStr">
         <is>
@@ -2485,9 +2513,10 @@
       <c r="D21" s="45" t="n"/>
       <c r="E21" s="45" t="n"/>
       <c r="F21" s="46" t="n"/>
-      <c r="G21" s="47">
-        <f>SUM(G7:G19)</f>
-        <v/>
+      <c r="G21" s="58" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="H21" s="47">
         <f>SUM(H7:H19)</f>
@@ -2514,8 +2543,13 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
+    <row r="22">
+      <c r="B22" s="59" t="inlineStr">
+        <is>
+          <t>Unit Price has no meaningful total — CLINs use different units (MO, HR, LOT). Year columns and Total are the real rollups.</t>
+        </is>
+      </c>
+    </row>
     <row r="24" ht="27.75" customHeight="1" s="28">
       <c r="B24" s="48" t="inlineStr">
         <is>
@@ -2936,8 +2970,6 @@
       </c>
       <c r="H40" s="50" t="n"/>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="27.75" customHeight="1" s="28">
       <c r="B43" s="48" t="inlineStr">
         <is>

--- a/products/pack2-proposal-toolkit/pricing-volume-checklist.xlsx
+++ b/products/pack2-proposal-toolkit/pricing-volume-checklist.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLIN Pricing Template" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Realism Self-Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -143,8 +143,44 @@
       <color rgb="FF0D1B2A"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0001696F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -169,8 +205,18 @@
         <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D1B2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -237,6 +283,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -248,7 +308,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -417,6 +477,55 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,7 +535,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -466,6 +575,45 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1944,1131 +2092,936 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <tabColor rgb="FF01696F"/>
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:M49"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:H40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="27" min="1" max="1"/>
-    <col width="28" customWidth="1" style="27" min="2" max="2"/>
-    <col width="14" customWidth="1" style="27" min="3" max="12"/>
-    <col width="16" customWidth="1" style="27" min="13" max="13"/>
+    <col width="2.5" customWidth="1" style="28" min="1" max="1"/>
+    <col width="16" customWidth="1" style="28" min="2" max="2"/>
+    <col width="42" customWidth="1" style="28" min="3" max="3"/>
+    <col width="42" customWidth="1" style="28" min="4" max="4"/>
+    <col width="42" customWidth="1" style="28" min="5" max="5"/>
+    <col width="12" customWidth="1" style="28" min="6" max="6"/>
+    <col width="14" customWidth="1" style="28" min="7" max="7"/>
+    <col width="36" customWidth="1" style="28" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="28">
-      <c r="B2" s="29" t="inlineStr">
-        <is>
-          <t>CLIN/SLIN PRICING TABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="28">
-      <c r="B3" s="30" t="inlineStr">
-        <is>
-          <t>Acqlerate — Defense Acquisitions Academy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="28">
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>Customize this template to match your RFP's CLIN structure. Formulas auto-calculate totals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" s="28">
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>CLIN/SLIN</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>Contract
-Type</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="G6" s="36" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="H6" s="36" t="inlineStr">
-        <is>
-          <t>Base Year</t>
-        </is>
-      </c>
-      <c r="I6" s="36" t="inlineStr">
-        <is>
-          <t>Option Yr 1</t>
-        </is>
-      </c>
-      <c r="J6" s="36" t="inlineStr">
-        <is>
-          <t>Option Yr 2</t>
-        </is>
-      </c>
-      <c r="K6" s="36" t="inlineStr">
-        <is>
-          <t>Option Yr 3</t>
-        </is>
-      </c>
-      <c r="L6" s="36" t="inlineStr">
-        <is>
-          <t>Option Yr 4</t>
-        </is>
-      </c>
-      <c r="M6" s="36" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" s="28">
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="C7" s="38" t="inlineStr">
-        <is>
-          <t>Program Management</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="inlineStr">
-        <is>
-          <t>FFP</t>
-        </is>
-      </c>
-      <c r="E7" s="37" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="F7" s="37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="42" t="n"/>
-      <c r="H7" s="42" t="n"/>
-      <c r="I7" s="42" t="n"/>
-      <c r="J7" s="42" t="n"/>
-      <c r="K7" s="42" t="n"/>
-      <c r="L7" s="42" t="n"/>
-      <c r="M7" s="43">
-        <f>SUM(H7:L7)</f>
+    <row r="2">
+      <c r="B2" s="60" t="inlineStr">
+        <is>
+          <t>Cost Realism Self-Check: Would the Government Believe Your Price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="28">
+      <c r="B3" s="61" t="inlineStr">
+        <is>
+          <t>The questions a DoD cost/price analyst asks under FAR 15.404-1(d). Answer each before submission. A low price the government does not believe gets adjusted upward for evaluation, and you lose the advantage you cut margin for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="62" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
+        <is>
+          <t>The question the analyst asks</t>
+        </is>
+      </c>
+      <c r="D5" s="62" t="inlineStr">
+        <is>
+          <t>What a strong answer looks like</t>
+        </is>
+      </c>
+      <c r="E5" s="62" t="inlineStr">
+        <is>
+          <t>Typical finding if weak</t>
+        </is>
+      </c>
+      <c r="F5" s="62" t="inlineStr">
+        <is>
+          <t>Risk if weak</t>
+        </is>
+      </c>
+      <c r="G5" s="62" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="62" t="inlineStr">
+        <is>
+          <t>Your evidence / notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1" s="28">
+      <c r="B6" s="63" t="inlineStr">
+        <is>
+          <t>Labor rates</t>
+        </is>
+      </c>
+      <c r="C6" s="64" t="inlineStr">
+        <is>
+          <t>Are proposed labor rates realistic for the labor categories, the location, and the clearance level required?</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>Rates tied to a named source: BLS, GSA MAS, your forward pricing rate agreement, or current payroll for the same LCATs. A rate build-up per category.</t>
+        </is>
+      </c>
+      <c r="E6" s="65" t="inlineStr">
+        <is>
+          <t>Rates below market for cleared labor. Government adjusts upward to its own IGCE rate for evaluation; you lose the price advantage and gain a realism weakness.</t>
+        </is>
+      </c>
+      <c r="F6" s="66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H6" s="67" t="n"/>
+    </row>
+    <row r="7" ht="70" customHeight="1" s="28">
+      <c r="B7" s="68" t="inlineStr">
+        <is>
+          <t>Labor rates</t>
+        </is>
+      </c>
+      <c r="C7" s="69" t="inlineStr">
+        <is>
+          <t>Do the rates escalate over the period of performance, and is the escalation defensible?</t>
+        </is>
+      </c>
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>Annual escalation stated, with the basis (ECI, DoL wage determination, your actual history). Consistent across volumes.</t>
+        </is>
+      </c>
+      <c r="E7" s="70" t="inlineStr">
+        <is>
+          <t>Flat rates across five years. Analyst applies escalation for you and your evaluated price rises.</t>
+        </is>
+      </c>
+      <c r="F7" s="71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H7" s="72" t="n"/>
+    </row>
+    <row r="8" ht="70" customHeight="1" s="28">
+      <c r="B8" s="63" t="inlineStr">
+        <is>
+          <t>Labor hours</t>
+        </is>
+      </c>
+      <c r="C8" s="64" t="inlineStr">
+        <is>
+          <t>Are proposed hours sufficient to perform the PWS as your technical volume describes it?</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>A basis of estimate by task showing how hours were derived. Hours in the price volume match the staffing in the technical volume.</t>
+        </is>
+      </c>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>Technical volume promises 24/7 coverage or surge capacity; hours support one shift. The two volumes contradict each other.</t>
+        </is>
+      </c>
+      <c r="F8" s="66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H8" s="67" t="n"/>
+    </row>
+    <row r="9" ht="70" customHeight="1" s="28">
+      <c r="B9" s="68" t="inlineStr">
+        <is>
+          <t>Labor hours</t>
+        </is>
+      </c>
+      <c r="C9" s="69" t="inlineStr">
+        <is>
+          <t>Is the productive-hours assumption realistic?</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>Productive hours per FTE stated (typically 1,880 to 1,920 for a 2,080-hour year) with leave and training accounted for.</t>
+        </is>
+      </c>
+      <c r="E9" s="70" t="inlineStr">
+        <is>
+          <t>2,080 productive hours per FTE. Nobody works every hour of the year; the analyst knows it.</t>
+        </is>
+      </c>
+      <c r="F9" s="71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H9" s="72" t="n"/>
+    </row>
+    <row r="10" ht="70" customHeight="1" s="28">
+      <c r="B10" s="63" t="inlineStr">
+        <is>
+          <t>Labor mix</t>
+        </is>
+      </c>
+      <c r="C10" s="64" t="inlineStr">
+        <is>
+          <t>Does the labor mix (senior vs. junior) match the complexity described in the technical volume?</t>
+        </is>
+      </c>
+      <c r="D10" s="65" t="inlineStr">
+        <is>
+          <t>Mix justified by task. Senior hours where the technical volume says the work is hard.</t>
+        </is>
+      </c>
+      <c r="E10" s="65" t="inlineStr">
+        <is>
+          <t>A senior-heavy technical narrative priced with a junior-heavy team, or the reverse.</t>
+        </is>
+      </c>
+      <c r="F10" s="66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H10" s="67" t="n"/>
+    </row>
+    <row r="11" ht="70" customHeight="1" s="28">
+      <c r="B11" s="68" t="inlineStr">
+        <is>
+          <t>Uncompensated overtime</t>
+        </is>
+      </c>
+      <c r="C11" s="69" t="inlineStr">
+        <is>
+          <t>Are you relying on uncompensated overtime to make the price work?</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>Per FAR 52.237-10, disclose it if proposed. State the policy and show it is applied consistently, not just to this bid.</t>
+        </is>
+      </c>
+      <c r="E11" s="70" t="inlineStr">
+        <is>
+          <t>Undisclosed uncompensated overtime discovered in the rate build-up. Realism finding and a credibility problem.</t>
+        </is>
+      </c>
+      <c r="F11" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H11" s="72" t="n"/>
+    </row>
+    <row r="12" ht="70" customHeight="1" s="28">
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>Indirect rates</t>
+        </is>
+      </c>
+      <c r="C12" s="64" t="inlineStr">
+        <is>
+          <t>Are fringe, overhead, and G&amp;A consistent with your FPRA, FPRP, or most recent DCAA-accepted rates?</t>
+        </is>
+      </c>
+      <c r="D12" s="65" t="inlineStr">
+        <is>
+          <t>Rates match the agreement or are explained. If you are bidding below your accepted rates, say why and show it is sustainable.</t>
+        </is>
+      </c>
+      <c r="E12" s="65" t="inlineStr">
+        <is>
+          <t>Bid rates lower than your DCAA-accepted rates with no explanation. Analyst substitutes the accepted rates.</t>
+        </is>
+      </c>
+      <c r="F12" s="66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H12" s="67" t="n"/>
+    </row>
+    <row r="13" ht="70" customHeight="1" s="28">
+      <c r="B13" s="68" t="inlineStr">
+        <is>
+          <t>Indirect rates</t>
+        </is>
+      </c>
+      <c r="C13" s="69" t="inlineStr">
+        <is>
+          <t>Is the indirect rate base applied correctly (e.g., overhead on direct labor plus fringe, G&amp;A on total cost input)?</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Rate build-up shows each base explicitly. Consistent with your disclosed accounting practices.</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
+        <is>
+          <t>Overhead applied to a base that excludes fringe when your disclosure statement says it includes it. Recalculated for you.</t>
+        </is>
+      </c>
+      <c r="F13" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H13" s="72" t="n"/>
+    </row>
+    <row r="14" ht="70" customHeight="1" s="28">
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>Fee / profit</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>Is fee within the range the government will find reasonable for this contract type and risk?</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>Fee stated, with a weighted-guidelines rationale if cost-type. Consistent with contract type (lower for CPFF, higher for FFP risk).</t>
+        </is>
+      </c>
+      <c r="E14" s="65" t="inlineStr">
+        <is>
+          <t>A 15% fee on a low-risk CPFF. Reasonableness finding.</t>
+        </is>
+      </c>
+      <c r="F14" s="66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G14" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H14" s="67" t="n"/>
+    </row>
+    <row r="15" ht="70" customHeight="1" s="28">
+      <c r="B15" s="68" t="inlineStr">
+        <is>
+          <t>ODCs</t>
+        </is>
+      </c>
+      <c r="C15" s="69" t="inlineStr">
+        <is>
+          <t>Are all ODCs the PWS implies actually priced: travel, materials, software licenses, training, security clearances?</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>ODC schedule reconciled to the PWS and the technical volume. Travel by trip with JTR rates. Licenses by seat.</t>
+        </is>
+      </c>
+      <c r="E15" s="70" t="inlineStr">
+        <is>
+          <t>Travel described in the technical volume but not priced. Analyst adds it to your evaluated price.</t>
+        </is>
+      </c>
+      <c r="F15" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G15" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H15" s="72" t="n"/>
+    </row>
+    <row r="16" ht="70" customHeight="1" s="28">
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>ODCs</t>
+        </is>
+      </c>
+      <c r="C16" s="64" t="inlineStr">
+        <is>
+          <t>Is travel priced at current JTR per diem and GSA airfare?</t>
+        </is>
+      </c>
+      <c r="D16" s="65" t="inlineStr">
+        <is>
+          <t>Trip table: destination, duration, travelers, per diem source, airfare source.</t>
+        </is>
+      </c>
+      <c r="E16" s="65" t="inlineStr">
+        <is>
+          <t>A lump-sum travel line. Cannot be evaluated for realism; treated as unsupported.</t>
+        </is>
+      </c>
+      <c r="F16" s="66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G16" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H16" s="67" t="n"/>
+    </row>
+    <row r="17" ht="70" customHeight="1" s="28">
+      <c r="B17" s="68" t="inlineStr">
+        <is>
+          <t>Subcontracts</t>
+        </is>
+      </c>
+      <c r="C17" s="69" t="inlineStr">
+        <is>
+          <t>Are subcontractor costs supported by quotes or subcontractor cost proposals?</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>Quotes or sub proposals attached or available. Sub labor rates and hours visible if cost-type.</t>
+        </is>
+      </c>
+      <c r="E17" s="70" t="inlineStr">
+        <is>
+          <t>A subcontract line with no support. Treated as unsupported; may be excluded or adjusted.</t>
+        </is>
+      </c>
+      <c r="F17" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H17" s="72" t="n"/>
+    </row>
+    <row r="18" ht="70" customHeight="1" s="28">
+      <c r="B18" s="63" t="inlineStr">
+        <is>
+          <t>Subcontracts</t>
+        </is>
+      </c>
+      <c r="C18" s="64" t="inlineStr">
+        <is>
+          <t>Is your pass-through rate on subcontracts reasonable, and does it comply with DFARS 252.215-7009 if pass-through exceeds 70%?</t>
+        </is>
+      </c>
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>Pass-through stated. If excessive pass-through applies, the added-value narrative is written.</t>
+        </is>
+      </c>
+      <c r="E18" s="65" t="inlineStr">
+        <is>
+          <t>Prime adds G&amp;A and fee on a subcontract that is 80% of the work, with no added-value explanation.</t>
+        </is>
+      </c>
+      <c r="F18" s="66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G18" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H18" s="67" t="n"/>
+    </row>
+    <row r="19" ht="70" customHeight="1" s="28">
+      <c r="B19" s="68" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="C19" s="69" t="inlineStr">
+        <is>
+          <t>Does every number in the price volume trace to the technical and management volumes?</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>A cross-walk: staffing plan headcount equals priced FTEs; schedule duration equals priced period; deliverables equal priced hours.</t>
+        </is>
+      </c>
+      <c r="E19" s="70" t="inlineStr">
+        <is>
+          <t>Three volumes, three different headcounts. This is the single most common realism finding.</t>
+        </is>
+      </c>
+      <c r="F19" s="71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G19" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H19" s="72" t="n"/>
+    </row>
+    <row r="20" ht="70" customHeight="1" s="28">
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="C20" s="64" t="inlineStr">
+        <is>
+          <t>Are assumptions stated in one place and consistent with the RFP?</t>
+        </is>
+      </c>
+      <c r="D20" s="65" t="inlineStr">
+        <is>
+          <t>An assumptions section listing every pricing assumption. Nothing in the assumptions contradicts a PWS requirement.</t>
+        </is>
+      </c>
+      <c r="E20" s="65" t="inlineStr">
+        <is>
+          <t>An assumption that shifts a requirement to the government, buried in a footnote. Read as an exception to the terms.</t>
+        </is>
+      </c>
+      <c r="F20" s="66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G20" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H20" s="67" t="n"/>
+    </row>
+    <row r="21" ht="70" customHeight="1" s="28">
+      <c r="B21" s="68" t="inlineStr">
+        <is>
+          <t>Basis of estimate</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>Can every cost element be traced to a documented basis of estimate?</t>
+        </is>
+      </c>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>BOE per task or CLIN: method (engineering estimate, analogy, parametric, historical), source data, and the calculation.</t>
+        </is>
+      </c>
+      <c r="E21" s="70" t="inlineStr">
+        <is>
+          <t>Costs asserted without a method. Analyst cannot evaluate realism and marks it unsupported.</t>
+        </is>
+      </c>
+      <c r="F21" s="71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G21" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H21" s="72" t="n"/>
+    </row>
+    <row r="22" ht="70" customHeight="1" s="28">
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="C22" s="64" t="inlineStr">
+        <is>
+          <t>Is transition-in priced, and does the price match the transition plan's duration and staffing?</t>
+        </is>
+      </c>
+      <c r="D22" s="65" t="inlineStr">
+        <is>
+          <t>Transition CLIN or line item with hours and duration matching the transition plan in the technical volume.</t>
+        </is>
+      </c>
+      <c r="E22" s="65" t="inlineStr">
+        <is>
+          <t>A 60-day transition plan with no transition costs. Either the plan is unrealistic or the price is.</t>
+        </is>
+      </c>
+      <c r="F22" s="66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G22" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H22" s="67" t="n"/>
+    </row>
+    <row r="23" ht="70" customHeight="1" s="28">
+      <c r="B23" s="68" t="inlineStr">
+        <is>
+          <t>Contract type risk</t>
+        </is>
+      </c>
+      <c r="C23" s="69" t="inlineStr">
+        <is>
+          <t>Under FFP, have you priced the risk the technical volume takes on?</t>
+        </is>
+      </c>
+      <c r="D23" s="70" t="inlineStr">
+        <is>
+          <t>Contingency or risk-adjusted hours identified for the risks named in your own risk section.</t>
+        </is>
+      </c>
+      <c r="E23" s="70" t="inlineStr">
+        <is>
+          <t>An FFP price with no risk allowance, while the technical volume lists six significant risks.</t>
+        </is>
+      </c>
+      <c r="F23" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G23" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H23" s="72" t="n"/>
+    </row>
+    <row r="24" ht="70" customHeight="1" s="28">
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>Option years</t>
+        </is>
+      </c>
+      <c r="C24" s="64" t="inlineStr">
+        <is>
+          <t>Are option years priced consistently with the base, and do they reflect learning or escalation?</t>
+        </is>
+      </c>
+      <c r="D24" s="65" t="inlineStr">
+        <is>
+          <t>Option pricing shows the escalation basis and any efficiency assumed. Efficiencies explained.</t>
+        </is>
+      </c>
+      <c r="E24" s="65" t="inlineStr">
+        <is>
+          <t>Option years priced identically to the base with no escalation, or with a learning-curve discount that is not explained.</t>
+        </is>
+      </c>
+      <c r="F24" s="66" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G24" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H24" s="67" t="n"/>
+    </row>
+    <row r="25" ht="70" customHeight="1" s="28">
+      <c r="B25" s="68" t="inlineStr">
+        <is>
+          <t>CMMC / compliance</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>Are CMMC assessment, cybersecurity, and other compliance costs included where the contract requires them?</t>
+        </is>
+      </c>
+      <c r="D25" s="70" t="inlineStr">
+        <is>
+          <t>CMMC Level 2 C3PAO assessment cost (Phase 2 effective November 10, 2026), NIST 800-171 sustainment, and any FedRAMP or clearance costs priced as ODCs or in overhead, and stated.</t>
+        </is>
+      </c>
+      <c r="E25" s="70" t="inlineStr">
+        <is>
+          <t>Compliance costs omitted entirely. Realism finding, and a delivery risk if you win.</t>
+        </is>
+      </c>
+      <c r="F25" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G25" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H25" s="72" t="n"/>
+    </row>
+    <row r="26" ht="70" customHeight="1" s="28">
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="C26" s="64" t="inlineStr">
+        <is>
+          <t>Does the spreadsheet actually add up, and are formulas visible if requested?</t>
+        </is>
+      </c>
+      <c r="D26" s="65" t="inlineStr">
+        <is>
+          <t>Every total is a live formula. A recalculation has been run. Rounding stated. The file provided matches the PDF.</t>
+        </is>
+      </c>
+      <c r="E26" s="65" t="inlineStr">
+        <is>
+          <t>Hard-coded totals that do not sum. The analyst finds it in the first hour.</t>
+        </is>
+      </c>
+      <c r="F26" s="66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G26" s="66" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H26" s="67" t="n"/>
+    </row>
+    <row r="27" ht="70" customHeight="1" s="28">
+      <c r="B27" s="68" t="inlineStr">
+        <is>
+          <t>Certified cost data</t>
+        </is>
+      </c>
+      <c r="C27" s="69" t="inlineStr">
+        <is>
+          <t>If over the TINA threshold ($2.5M), is certified cost or pricing data provided, or an exemption claimed correctly?</t>
+        </is>
+      </c>
+      <c r="D27" s="70" t="inlineStr">
+        <is>
+          <t>Table 15-2 format if required. Exemption (adequate price competition, commercial item) stated with basis.</t>
+        </is>
+      </c>
+      <c r="E27" s="70" t="inlineStr">
+        <is>
+          <t>Missing certified data on a covered action. Proposal is incomplete.</t>
+        </is>
+      </c>
+      <c r="F27" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G27" s="71" t="inlineStr">
+        <is>
+          <t>Not Checked</t>
+        </is>
+      </c>
+      <c r="H27" s="72" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="73" t="inlineStr">
+        <is>
+          <t>READINESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="74" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="C30" s="75">
+        <f>COUNTA(C6:C27)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" s="28">
-      <c r="B8" s="41" t="inlineStr">
-        <is>
-          <t>0002</t>
-        </is>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
-        <is>
-          <t>Systems Engineering &amp; Technical Support</t>
-        </is>
-      </c>
-      <c r="D8" s="37" t="inlineStr">
-        <is>
-          <t>T&amp;M</t>
-        </is>
-      </c>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="42" t="n"/>
-      <c r="H8" s="42" t="n"/>
-      <c r="I8" s="42" t="n"/>
-      <c r="J8" s="42" t="n"/>
-      <c r="K8" s="42" t="n"/>
-      <c r="L8" s="42" t="n"/>
-      <c r="M8" s="43">
-        <f>SUM(H8:L8)</f>
+    <row r="31">
+      <c r="B31" s="74" t="inlineStr">
+        <is>
+          <t>Supported</t>
+        </is>
+      </c>
+      <c r="C31" s="75">
+        <f>COUNTIF(G6:G27,"Supported")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" s="28">
-      <c r="B9" s="41" t="inlineStr">
-        <is>
-          <t>0002AA</t>
-        </is>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  — Senior Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="inlineStr">
-        <is>
-          <t>T&amp;M</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="42" t="n"/>
-      <c r="H9" s="42" t="n"/>
-      <c r="I9" s="42" t="n"/>
-      <c r="J9" s="42" t="n"/>
-      <c r="K9" s="42" t="n"/>
-      <c r="L9" s="42" t="n"/>
-      <c r="M9" s="43">
-        <f>SUM(H9:L9)</f>
+    <row r="32">
+      <c r="B32" s="74" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="C32" s="75">
+        <f>COUNTIF(G6:G27,"Weak")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" s="28">
-      <c r="B10" s="41" t="inlineStr">
-        <is>
-          <t>0002AB</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  — Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D10" s="37" t="inlineStr">
-        <is>
-          <t>T&amp;M</t>
-        </is>
-      </c>
-      <c r="E10" s="37" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="42" t="n"/>
-      <c r="H10" s="42" t="n"/>
-      <c r="I10" s="42" t="n"/>
-      <c r="J10" s="42" t="n"/>
-      <c r="K10" s="42" t="n"/>
-      <c r="L10" s="42" t="n"/>
-      <c r="M10" s="43">
-        <f>SUM(H10:L10)</f>
+    <row r="33">
+      <c r="B33" s="74" t="inlineStr">
+        <is>
+          <t>Not yet checked</t>
+        </is>
+      </c>
+      <c r="C33" s="75">
+        <f>COUNTIF(G6:G27,"Not Checked")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" s="28">
-      <c r="B11" s="41" t="inlineStr">
-        <is>
-          <t>0002AC</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  — Junior Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>T&amp;M</t>
-        </is>
-      </c>
-      <c r="E11" s="37" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="42" t="n"/>
-      <c r="H11" s="42" t="n"/>
-      <c r="I11" s="42" t="n"/>
-      <c r="J11" s="42" t="n"/>
-      <c r="K11" s="42" t="n"/>
-      <c r="L11" s="42" t="n"/>
-      <c r="M11" s="43">
-        <f>SUM(H11:L11)</f>
+    <row r="34">
+      <c r="B34" s="74" t="inlineStr">
+        <is>
+          <t>High-risk items still Weak or unchecked</t>
+        </is>
+      </c>
+      <c r="C34" s="75">
+        <f>COUNTIFS(F6:F27,"High",G6:G27,"Weak")+COUNTIFS(F6:F27,"High",G6:G27,"Not Checked")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" s="28">
-      <c r="B12" s="41" t="inlineStr">
-        <is>
-          <t>0003</t>
-        </is>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>Cybersecurity Operations</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>FFP</t>
-        </is>
-      </c>
-      <c r="E12" s="37" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G12" s="42" t="n"/>
-      <c r="H12" s="42" t="n"/>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="42" t="n"/>
-      <c r="K12" s="42" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="43">
-        <f>SUM(H12:L12)</f>
+    <row r="35">
+      <c r="B35" s="74" t="inlineStr">
+        <is>
+          <t>% supported (excl. N/A)</t>
+        </is>
+      </c>
+      <c r="C35" s="76">
+        <f>IF((C30-COUNTIF(G6:G27,"N/A"))=0,0,C31/(C30-COUNTIF(G6:G27,"N/A")))</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" s="28">
-      <c r="B13" s="41" t="inlineStr">
-        <is>
-          <t>0004</t>
-        </is>
-      </c>
-      <c r="C13" s="38" t="inlineStr">
-        <is>
-          <t>Cloud Migration Services</t>
-        </is>
-      </c>
-      <c r="D13" s="37" t="inlineStr">
-        <is>
-          <t>CPFF</t>
-        </is>
-      </c>
-      <c r="E13" s="37" t="inlineStr">
-        <is>
-          <t>LOT</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="42" t="n"/>
-      <c r="H13" s="42" t="n"/>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="42" t="n"/>
-      <c r="K13" s="42" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="43">
-        <f>SUM(H13:L13)</f>
+    <row r="36">
+      <c r="B36" s="74" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C36" s="77">
+        <f>IF(C34&gt;0,"NOT READY: high-risk items open",IF(C32&gt;0,"AT RISK: weak items remain",IF(C33&gt;0,"INCOMPLETE: items unchecked","READY TO SUBMIT")))</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" s="28">
-      <c r="B14" s="41" t="inlineStr">
-        <is>
-          <t>0005</t>
-        </is>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>Help Desk / Service Desk (Tier I-III)</t>
-        </is>
-      </c>
-      <c r="D14" s="37" t="inlineStr">
-        <is>
-          <t>FFP</t>
-        </is>
-      </c>
-      <c r="E14" s="37" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="F14" s="37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G14" s="42" t="n"/>
-      <c r="H14" s="42" t="n"/>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="42" t="n"/>
-      <c r="K14" s="42" t="n"/>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="43">
-        <f>SUM(H14:L14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" s="28">
-      <c r="B15" s="41" t="inlineStr">
-        <is>
-          <t>0006</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>NTE</t>
-        </is>
-      </c>
-      <c r="E15" s="37" t="inlineStr">
-        <is>
-          <t>LOT</t>
-        </is>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G15" s="42" t="n"/>
-      <c r="H15" s="42" t="n"/>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="43">
-        <f>SUM(H15:L15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" s="28">
-      <c r="B16" s="41" t="inlineStr">
-        <is>
-          <t>0007</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>Other Direct Costs (Materials, Licenses)</t>
-        </is>
-      </c>
-      <c r="D16" s="37" t="inlineStr">
-        <is>
-          <t>NTE</t>
-        </is>
-      </c>
-      <c r="E16" s="37" t="inlineStr">
-        <is>
-          <t>LOT</t>
-        </is>
-      </c>
-      <c r="F16" s="37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="42" t="n"/>
-      <c r="H16" s="42" t="n"/>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="42" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="43">
-        <f>SUM(H16:L16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" s="28">
-      <c r="B17" s="41" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="C17" s="38" t="inlineStr">
-        <is>
-          <t>Program Management (Option Year 1)</t>
-        </is>
-      </c>
-      <c r="D17" s="37" t="inlineStr">
-        <is>
-          <t>FFP</t>
-        </is>
-      </c>
-      <c r="E17" s="37" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="F17" s="37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G17" s="42" t="n"/>
-      <c r="H17" s="42" t="n"/>
-      <c r="I17" s="42" t="n"/>
-      <c r="J17" s="42" t="n"/>
-      <c r="K17" s="42" t="n"/>
-      <c r="L17" s="42" t="n"/>
-      <c r="M17" s="43">
-        <f>SUM(H17:L17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="28">
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>Systems Engineering &amp; Technical Support (OY1)</t>
-        </is>
-      </c>
-      <c r="D18" s="37" t="inlineStr">
-        <is>
-          <t>T&amp;M</t>
-        </is>
-      </c>
-      <c r="E18" s="37" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F18" s="37" t="n"/>
-      <c r="G18" s="42" t="n"/>
-      <c r="H18" s="42" t="n"/>
-      <c r="I18" s="42" t="n"/>
-      <c r="J18" s="42" t="n"/>
-      <c r="K18" s="42" t="n"/>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="43">
-        <f>SUM(H18:L18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" s="28">
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="C19" s="38" t="inlineStr">
-        <is>
-          <t>Cybersecurity Operations (OY1)</t>
-        </is>
-      </c>
-      <c r="D19" s="37" t="inlineStr">
-        <is>
-          <t>FFP</t>
-        </is>
-      </c>
-      <c r="E19" s="37" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="F19" s="37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G19" s="42" t="n"/>
-      <c r="H19" s="42" t="n"/>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42" t="n"/>
-      <c r="K19" s="42" t="n"/>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="43">
-        <f>SUM(H19:L19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1" s="28">
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="n"/>
-      <c r="D21" s="45" t="n"/>
-      <c r="E21" s="45" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="58" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H21" s="47">
-        <f>SUM(H7:H19)</f>
-        <v/>
-      </c>
-      <c r="I21" s="47">
-        <f>SUM(I7:I19)</f>
-        <v/>
-      </c>
-      <c r="J21" s="47">
-        <f>SUM(J7:J19)</f>
-        <v/>
-      </c>
-      <c r="K21" s="47">
-        <f>SUM(K7:K19)</f>
-        <v/>
-      </c>
-      <c r="L21" s="47">
-        <f>SUM(L7:L19)</f>
-        <v/>
-      </c>
-      <c r="M21" s="47">
-        <f>SUM(M7:M19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="59" t="inlineStr">
-        <is>
-          <t>Unit Price has no meaningful total — CLINs use different units (MO, HR, LOT). Year columns and Total are the real rollups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="27.75" customHeight="1" s="28">
-      <c r="B24" s="48" t="inlineStr">
-        <is>
-          <t>LABOR CATEGORY RATE SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="31.5" customHeight="1" s="28">
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>LCAT</t>
-        </is>
-      </c>
-      <c r="C25" s="36" t="inlineStr">
-        <is>
-          <t>Base Year
-Rate</t>
-        </is>
-      </c>
-      <c r="D25" s="36" t="inlineStr">
-        <is>
-          <t>OY1 Rate</t>
-        </is>
-      </c>
-      <c r="E25" s="36" t="inlineStr">
-        <is>
-          <t>OY2 Rate</t>
-        </is>
-      </c>
-      <c r="F25" s="36" t="inlineStr">
-        <is>
-          <t>OY3 Rate</t>
-        </is>
-      </c>
-      <c r="G25" s="36" t="inlineStr">
-        <is>
-          <t>OY4 Rate</t>
-        </is>
-      </c>
-      <c r="H25" s="36" t="inlineStr">
-        <is>
-          <t>Escalation %</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="28">
-      <c r="B26" s="49" t="inlineStr">
-        <is>
-          <t>Program Manager</t>
-        </is>
-      </c>
-      <c r="C26" s="42" t="n"/>
-      <c r="D26" s="42">
-        <f>IF(C26="","",C26*(1+H26))</f>
-        <v/>
-      </c>
-      <c r="E26" s="42">
-        <f>IF(C26="","",C26*(1+H26)^2)</f>
-        <v/>
-      </c>
-      <c r="F26" s="42">
-        <f>IF(C26="","",C26*(1+H26)^3)</f>
-        <v/>
-      </c>
-      <c r="G26" s="42">
-        <f>IF(C26="","",C26*(1+H26)^4)</f>
-        <v/>
-      </c>
-      <c r="H26" s="50" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="28">
-      <c r="B27" s="49" t="inlineStr">
-        <is>
-          <t>Deputy Program Manager</t>
-        </is>
-      </c>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42">
-        <f>IF(C27="","",C27*(1+H27))</f>
-        <v/>
-      </c>
-      <c r="E27" s="42">
-        <f>IF(C27="","",C27*(1+H27)^2)</f>
-        <v/>
-      </c>
-      <c r="F27" s="42">
-        <f>IF(C27="","",C27*(1+H27)^3)</f>
-        <v/>
-      </c>
-      <c r="G27" s="42">
-        <f>IF(C27="","",C27*(1+H27)^4)</f>
-        <v/>
-      </c>
-      <c r="H27" s="50" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="28">
-      <c r="B28" s="49" t="inlineStr">
-        <is>
-          <t>Senior Systems Engineer</t>
-        </is>
-      </c>
-      <c r="C28" s="42" t="n"/>
-      <c r="D28" s="42">
-        <f>IF(C28="","",C28*(1+H28))</f>
-        <v/>
-      </c>
-      <c r="E28" s="42">
-        <f>IF(C28="","",C28*(1+H28)^2)</f>
-        <v/>
-      </c>
-      <c r="F28" s="42">
-        <f>IF(C28="","",C28*(1+H28)^3)</f>
-        <v/>
-      </c>
-      <c r="G28" s="42">
-        <f>IF(C28="","",C28*(1+H28)^4)</f>
-        <v/>
-      </c>
-      <c r="H28" s="50" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="28">
-      <c r="B29" s="49" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="C29" s="42" t="n"/>
-      <c r="D29" s="42">
-        <f>IF(C29="","",C29*(1+H29))</f>
-        <v/>
-      </c>
-      <c r="E29" s="42">
-        <f>IF(C29="","",C29*(1+H29)^2)</f>
-        <v/>
-      </c>
-      <c r="F29" s="42">
-        <f>IF(C29="","",C29*(1+H29)^3)</f>
-        <v/>
-      </c>
-      <c r="G29" s="42">
-        <f>IF(C29="","",C29*(1+H29)^4)</f>
-        <v/>
-      </c>
-      <c r="H29" s="50" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="28">
-      <c r="B30" s="49" t="inlineStr">
-        <is>
-          <t>Junior Systems Engineer</t>
-        </is>
-      </c>
-      <c r="C30" s="42" t="n"/>
-      <c r="D30" s="42">
-        <f>IF(C30="","",C30*(1+H30))</f>
-        <v/>
-      </c>
-      <c r="E30" s="42">
-        <f>IF(C30="","",C30*(1+H30)^2)</f>
-        <v/>
-      </c>
-      <c r="F30" s="42">
-        <f>IF(C30="","",C30*(1+H30)^3)</f>
-        <v/>
-      </c>
-      <c r="G30" s="42">
-        <f>IF(C30="","",C30*(1+H30)^4)</f>
-        <v/>
-      </c>
-      <c r="H30" s="50" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="28">
-      <c r="B31" s="49" t="inlineStr">
-        <is>
-          <t>Cybersecurity Analyst (Senior)</t>
-        </is>
-      </c>
-      <c r="C31" s="42" t="n"/>
-      <c r="D31" s="42">
-        <f>IF(C31="","",C31*(1+H31))</f>
-        <v/>
-      </c>
-      <c r="E31" s="42">
-        <f>IF(C31="","",C31*(1+H31)^2)</f>
-        <v/>
-      </c>
-      <c r="F31" s="42">
-        <f>IF(C31="","",C31*(1+H31)^3)</f>
-        <v/>
-      </c>
-      <c r="G31" s="42">
-        <f>IF(C31="","",C31*(1+H31)^4)</f>
-        <v/>
-      </c>
-      <c r="H31" s="50" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="28">
-      <c r="B32" s="49" t="inlineStr">
-        <is>
-          <t>Cybersecurity Analyst</t>
-        </is>
-      </c>
-      <c r="C32" s="42" t="n"/>
-      <c r="D32" s="42">
-        <f>IF(C32="","",C32*(1+H32))</f>
-        <v/>
-      </c>
-      <c r="E32" s="42">
-        <f>IF(C32="","",C32*(1+H32)^2)</f>
-        <v/>
-      </c>
-      <c r="F32" s="42">
-        <f>IF(C32="","",C32*(1+H32)^3)</f>
-        <v/>
-      </c>
-      <c r="G32" s="42">
-        <f>IF(C32="","",C32*(1+H32)^4)</f>
-        <v/>
-      </c>
-      <c r="H32" s="50" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="28">
-      <c r="B33" s="49" t="inlineStr">
-        <is>
-          <t>Cloud Architect</t>
-        </is>
-      </c>
-      <c r="C33" s="42" t="n"/>
-      <c r="D33" s="42">
-        <f>IF(C33="","",C33*(1+H33))</f>
-        <v/>
-      </c>
-      <c r="E33" s="42">
-        <f>IF(C33="","",C33*(1+H33)^2)</f>
-        <v/>
-      </c>
-      <c r="F33" s="42">
-        <f>IF(C33="","",C33*(1+H33)^3)</f>
-        <v/>
-      </c>
-      <c r="G33" s="42">
-        <f>IF(C33="","",C33*(1+H33)^4)</f>
-        <v/>
-      </c>
-      <c r="H33" s="50" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="28">
-      <c r="B34" s="49" t="inlineStr">
-        <is>
-          <t>Help Desk Specialist (Tier I)</t>
-        </is>
-      </c>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42">
-        <f>IF(C34="","",C34*(1+H34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="42">
-        <f>IF(C34="","",C34*(1+H34)^2)</f>
-        <v/>
-      </c>
-      <c r="F34" s="42">
-        <f>IF(C34="","",C34*(1+H34)^3)</f>
-        <v/>
-      </c>
-      <c r="G34" s="42">
-        <f>IF(C34="","",C34*(1+H34)^4)</f>
-        <v/>
-      </c>
-      <c r="H34" s="50" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="28">
-      <c r="B35" s="49" t="inlineStr">
-        <is>
-          <t>Help Desk Specialist (Tier II)</t>
-        </is>
-      </c>
-      <c r="C35" s="42" t="n"/>
-      <c r="D35" s="42">
-        <f>IF(C35="","",C35*(1+H35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="42">
-        <f>IF(C35="","",C35*(1+H35)^2)</f>
-        <v/>
-      </c>
-      <c r="F35" s="42">
-        <f>IF(C35="","",C35*(1+H35)^3)</f>
-        <v/>
-      </c>
-      <c r="G35" s="42">
-        <f>IF(C35="","",C35*(1+H35)^4)</f>
-        <v/>
-      </c>
-      <c r="H35" s="50" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="28">
-      <c r="B36" s="49" t="inlineStr">
-        <is>
-          <t>Help Desk Specialist (Tier III)</t>
-        </is>
-      </c>
-      <c r="C36" s="42" t="n"/>
-      <c r="D36" s="42">
-        <f>IF(C36="","",C36*(1+H36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="42">
-        <f>IF(C36="","",C36*(1+H36)^2)</f>
-        <v/>
-      </c>
-      <c r="F36" s="42">
-        <f>IF(C36="","",C36*(1+H36)^3)</f>
-        <v/>
-      </c>
-      <c r="G36" s="42">
-        <f>IF(C36="","",C36*(1+H36)^4)</f>
-        <v/>
-      </c>
-      <c r="H36" s="50" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="28">
-      <c r="B37" s="49" t="inlineStr">
-        <is>
-          <t>Database Administrator</t>
-        </is>
-      </c>
-      <c r="C37" s="42" t="n"/>
-      <c r="D37" s="42">
-        <f>IF(C37="","",C37*(1+H37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="42">
-        <f>IF(C37="","",C37*(1+H37)^2)</f>
-        <v/>
-      </c>
-      <c r="F37" s="42">
-        <f>IF(C37="","",C37*(1+H37)^3)</f>
-        <v/>
-      </c>
-      <c r="G37" s="42">
-        <f>IF(C37="","",C37*(1+H37)^4)</f>
-        <v/>
-      </c>
-      <c r="H37" s="50" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="28">
-      <c r="B38" s="49" t="inlineStr">
-        <is>
-          <t>Technical Writer</t>
-        </is>
-      </c>
-      <c r="C38" s="42" t="n"/>
-      <c r="D38" s="42">
-        <f>IF(C38="","",C38*(1+H38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="42">
-        <f>IF(C38="","",C38*(1+H38)^2)</f>
-        <v/>
-      </c>
-      <c r="F38" s="42">
-        <f>IF(C38="","",C38*(1+H38)^3)</f>
-        <v/>
-      </c>
-      <c r="G38" s="42">
-        <f>IF(C38="","",C38*(1+H38)^4)</f>
-        <v/>
-      </c>
-      <c r="H38" s="50" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="28">
-      <c r="B39" s="49" t="inlineStr">
-        <is>
-          <t>Quality Assurance Analyst</t>
-        </is>
-      </c>
-      <c r="C39" s="42" t="n"/>
-      <c r="D39" s="42">
-        <f>IF(C39="","",C39*(1+H39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="42">
-        <f>IF(C39="","",C39*(1+H39)^2)</f>
-        <v/>
-      </c>
-      <c r="F39" s="42">
-        <f>IF(C39="","",C39*(1+H39)^3)</f>
-        <v/>
-      </c>
-      <c r="G39" s="42">
-        <f>IF(C39="","",C39*(1+H39)^4)</f>
-        <v/>
-      </c>
-      <c r="H39" s="50" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="28">
-      <c r="B40" s="49" t="inlineStr">
-        <is>
-          <t>Administrative Support</t>
-        </is>
-      </c>
-      <c r="C40" s="42" t="n"/>
-      <c r="D40" s="42">
-        <f>IF(C40="","",C40*(1+H40))</f>
-        <v/>
-      </c>
-      <c r="E40" s="42">
-        <f>IF(C40="","",C40*(1+H40)^2)</f>
-        <v/>
-      </c>
-      <c r="F40" s="42">
-        <f>IF(C40="","",C40*(1+H40)^3)</f>
-        <v/>
-      </c>
-      <c r="G40" s="42">
-        <f>IF(C40="","",C40*(1+H40)^4)</f>
-        <v/>
-      </c>
-      <c r="H40" s="50" t="n"/>
-    </row>
-    <row r="43" ht="27.75" customHeight="1" s="28">
-      <c r="B43" s="48" t="inlineStr">
-        <is>
-          <t>INDIRECT RATE BUILD-UP</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1" s="28">
-      <c r="B44" s="51" t="inlineStr">
-        <is>
-          <t>Direct Labor Rate (Base):</t>
-        </is>
-      </c>
-      <c r="C44" s="52" t="n"/>
-      <c r="D44" s="53" t="inlineStr">
-        <is>
-          <t>Enter direct hourly or annual rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" s="28">
-      <c r="B45" s="51" t="inlineStr">
-        <is>
-          <t>Fringe Benefit Rate:</t>
-        </is>
-      </c>
-      <c r="C45" s="54" t="n"/>
-      <c r="D45" s="53" t="inlineStr">
-        <is>
-          <t>e.g., 32.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1" s="28">
-      <c r="B46" s="51" t="inlineStr">
-        <is>
-          <t>Overhead Rate:</t>
-        </is>
-      </c>
-      <c r="C46" s="54" t="n"/>
-      <c r="D46" s="53" t="inlineStr">
-        <is>
-          <t>e.g., 45.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="24" customHeight="1" s="28">
-      <c r="B47" s="51" t="inlineStr">
-        <is>
-          <t>G&amp;A Rate:</t>
-        </is>
-      </c>
-      <c r="C47" s="54" t="n"/>
-      <c r="D47" s="53" t="inlineStr">
-        <is>
-          <t>e.g., 12.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1" s="28">
-      <c r="B48" s="51" t="inlineStr">
-        <is>
-          <t>Fee/Profit:</t>
-        </is>
-      </c>
-      <c r="C48" s="54" t="n"/>
-      <c r="D48" s="53" t="inlineStr">
-        <is>
-          <t>e.g., 8.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1" s="28">
-      <c r="B49" s="51" t="inlineStr">
-        <is>
-          <t>Fully Burdened Rate:</t>
-        </is>
-      </c>
-      <c r="C49" s="55">
-        <f>IF(C44="","",C44*(1+C45)*(1+C46)*(1+C47)*(1+C48))</f>
-        <v/>
-      </c>
-      <c r="D49" s="53" t="inlineStr">
-        <is>
-          <t>Base × (1 + Fringe) × (1 + OH) × (1 + G&amp;A) × (1 + Fee)</t>
+    <row r="38" ht="42" customHeight="1" s="28">
+      <c r="B38" s="78" t="inlineStr">
+        <is>
+          <t>FAR 15.404-1(d): cost realism analysis determines whether the estimated proposed cost elements are realistic for the work to be performed, reflect a clear understanding of the requirements, and are consistent with the unique methods of performance described in the technical proposal. That last clause is where most proposals fail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="59" t="inlineStr">
+        <is>
+          <t>Acqlerate Proposal Toolkit · acqlerate.com · September 2026 Edition · Reflects FAC 2025-06</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B24:H24"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B38:H38"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <conditionalFormatting sqref="G6:G27">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>G6="Supported"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="4">
+      <formula>G6="Weak"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F27">
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>F6="High"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36">
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>LEFT(C36,9)="NOT READY"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="6">
+      <formula>OR(LEFT(C36,7)="AT RISK",LEFT(C36,10)="INCOMPLETE")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="3">
+      <formula>C36="READY TO SUBMIT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="F6:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6:G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Checked,Supported,Weak,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>